--- a/results/Topological Features.xlsx
+++ b/results/Topological Features.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\SECT算法及对比分析_2英文\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\sect修订中2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358A27CC-62E0-4991-AD01-9461A178558D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D132AF-7DCF-4FEE-B88D-5DD4E7E5EFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="100" windowWidth="18990" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8680" yWindow="100" windowWidth="10520" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
     <t>email-Eu-core</t>
   </si>
   <si>
-    <t>g22</t>
-  </si>
-  <si>
     <t>tree</t>
   </si>
   <si>
@@ -59,6 +56,10 @@
   </si>
   <si>
     <t>Clustering Coefficient</t>
+  </si>
+  <si>
+    <t>LFR_base</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -438,24 +439,24 @@
     <col min="1" max="1" width="17.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="56" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3">
         <v>55</v>
@@ -472,7 +473,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>100</v>
@@ -484,24 +485,24 @@
         <v>2</v>
       </c>
       <c r="E3" s="2">
-        <v>3.1E-2</v>
+        <v>3.0999999999999999E-3</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C4" s="2">
-        <v>1219</v>
+        <v>935</v>
       </c>
       <c r="D4" s="2">
-        <v>8.8655000000000008</v>
+        <v>6.2332999999999998</v>
       </c>
       <c r="E4" s="2">
-        <v>2.5000000000000001E-2</v>
+        <v>0.1867</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -512,18 +513,18 @@
         <v>1005</v>
       </c>
       <c r="C5" s="2">
-        <v>16706</v>
+        <v>16064</v>
       </c>
       <c r="D5" s="2">
-        <v>33.245800000000003</v>
+        <v>31.962800000000001</v>
       </c>
       <c r="E5" s="2">
-        <v>0.39939999999999998</v>
+        <v>0.39935500000000002</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3">
         <v>2884</v>
@@ -535,15 +536,15 @@
         <v>43.227499999999999</v>
       </c>
       <c r="E6" s="3">
-        <v>0.58599599999999996</v>
+        <v>0.58599999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3">
-        <v>49223</v>
+        <v>49236</v>
       </c>
       <c r="C7" s="3">
         <v>298335</v>
